--- a/master/result/43_重生商女_从贫穷到商业女王/43_重生商女_从贫穷到商业女王.xlsx
+++ b/master/result/43_重生商女_从贫穷到商业女王/43_重生商女_从贫穷到商业女王.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>street</v>
       </c>
       <c r="B2" t="str">
-        <v>street</v>
+        <v>/street/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>街道</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>poverty</v>
       </c>
       <c r="B3" t="str">
-        <v>poverty</v>
+        <v>/poverty/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>贫穷</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>solitary</v>
       </c>
       <c r="B4" t="str">
-        <v>solitary</v>
+        <v>/solitary/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>孤独的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>resolution</v>
       </c>
       <c r="B5" t="str">
-        <v>resolution</v>
+        <v>/resolution/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>决心</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>weak</v>
       </c>
       <c r="B6" t="str">
-        <v>weak</v>
+        <v>/weak/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>虚弱的</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>petroleum</v>
       </c>
       <c r="B7" t="str">
-        <v>petroleum</v>
+        <v>/petroleum/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>石油</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>learned</v>
       </c>
       <c r="B8" t="str">
-        <v>learned</v>
+        <v>/learned/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>博学的</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>yes</v>
       </c>
       <c r="B9" t="str">
-        <v>yes</v>
+        <v>/yes/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>是</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>exercise</v>
       </c>
       <c r="B10" t="str">
-        <v>exercise</v>
+        <v>/ˈeksəsaɪz/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>练习</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>human</v>
       </c>
       <c r="B11" t="str">
-        <v>human</v>
+        <v>/human/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>人</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>coal</v>
       </c>
       <c r="B12" t="str">
-        <v>coal</v>
+        <v>/kəʊl/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>煤</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>review</v>
       </c>
       <c r="B13" t="str">
-        <v>review</v>
+        <v>/rɪˈvjuː/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>复习</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>principal</v>
       </c>
       <c r="B14" t="str">
-        <v>principal</v>
+        <v>/principal/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>负责人</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>postcard</v>
       </c>
       <c r="B15" t="str">
-        <v>postcard</v>
+        <v>/postcard/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>明信片</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>celebrate</v>
       </c>
       <c r="B16" t="str">
-        <v>celebrate</v>
+        <v>/ˈselɪbreɪt/</v>
       </c>
       <c r="C16" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D16" t="str">
         <v>庆祝</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>woman</v>
       </c>
       <c r="B17" t="str">
-        <v>woman</v>
+        <v>/woman/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>妇女</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>thumb</v>
       </c>
       <c r="B18" t="str">
-        <v>thumb</v>
+        <v>/thumb/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>拇指</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>fund</v>
       </c>
       <c r="B19" t="str">
-        <v>fund</v>
+        <v>/fund/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>资金</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>companion</v>
       </c>
       <c r="B20" t="str">
-        <v>companion</v>
+        <v>/kəmˈpæniən/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>同伴</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>speciality</v>
       </c>
       <c r="B21" t="str">
-        <v>speciality</v>
+        <v>/speciality/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>专业</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>tool</v>
       </c>
       <c r="B22" t="str">
-        <v>tool</v>
+        <v>/tool/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>工具</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>space</v>
       </c>
       <c r="B23" t="str">
-        <v>space</v>
+        <v>/space/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>余地</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>fruit</v>
       </c>
       <c r="B24" t="str">
-        <v>fruit</v>
+        <v>/fruit/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>水果</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>ripe</v>
       </c>
       <c r="B25" t="str">
-        <v>ripe</v>
+        <v>/ripe/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>成熟的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>goose</v>
       </c>
       <c r="B26" t="str">
-        <v>goose</v>
+        <v>/goose/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>鹅</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>polar</v>
       </c>
       <c r="B27" t="str">
-        <v>polar</v>
+        <v>/polar/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>极地的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>specimen</v>
       </c>
       <c r="B28" t="str">
-        <v>specimen</v>
+        <v>/specimen/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>标本</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>complication</v>
       </c>
       <c r="B29" t="str">
-        <v>complication</v>
+        <v>/complication/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>复杂</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>practice</v>
       </c>
       <c r="B30" t="str">
-        <v>practice</v>
+        <v>/ˈpræktɪs/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>实践</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>supplement</v>
       </c>
       <c r="B31" t="str">
-        <v>supplement</v>
+        <v>/supplement/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>补充</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>groan</v>
       </c>
       <c r="B32" t="str">
-        <v>groan</v>
+        <v>/groan/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>呻吟</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>pick</v>
       </c>
       <c r="B33" t="str">
-        <v>pick</v>
+        <v>/pɪk/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>挑选</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>vicinity</v>
       </c>
       <c r="B34" t="str">
-        <v>vicinity</v>
+        <v>/vicinity/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>附近</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>ceiling</v>
       </c>
       <c r="B35" t="str">
-        <v>ceiling</v>
+        <v>/ˈsiːlɪŋ/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>天花板</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>publicity</v>
       </c>
       <c r="B36" t="str">
-        <v>publicity</v>
+        <v>/publicity/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>宣传</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>bracket</v>
       </c>
       <c r="B37" t="str">
-        <v>bracket</v>
+        <v>/bracket/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>括号</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>plot</v>
       </c>
       <c r="B38" t="str">
-        <v>plot</v>
+        <v>/plot/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>秘密计划</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>vertical</v>
       </c>
       <c r="B39" t="str">
-        <v>vertical</v>
+        <v>/vertical/</v>
       </c>
       <c r="C39" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>垂直的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>glow</v>
       </c>
       <c r="B40" t="str">
-        <v>glow</v>
+        <v>/glow/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>发光</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>thrill</v>
       </c>
       <c r="B41" t="str">
-        <v>thrill</v>
+        <v>/thrill/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>激动</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>accommodation</v>
       </c>
       <c r="B42" t="str">
-        <v>accommodation</v>
+        <v>/accommodation/</v>
       </c>
       <c r="C42" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>住宿</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>otherwise</v>
       </c>
       <c r="B43" t="str">
-        <v>otherwise</v>
+        <v>/otherwise/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>在其他方面</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>blunder</v>
       </c>
       <c r="B44" t="str">
-        <v>blunder</v>
+        <v>/blunder/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>大错</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>warn</v>
       </c>
       <c r="B45" t="str">
-        <v>warn</v>
+        <v>/warn/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>警告</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>inevitable</v>
       </c>
       <c r="B46" t="str">
-        <v>inevitable</v>
+        <v>/inevitable/</v>
       </c>
       <c r="C46" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D46" t="str">
         <v>不可避免的</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>see</v>
       </c>
       <c r="B47" t="str">
-        <v>see</v>
+        <v>/siː/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>看见</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>neither</v>
       </c>
       <c r="B48" t="str">
-        <v>neither</v>
+        <v>/neither/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>两者都不</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>humid</v>
       </c>
       <c r="B49" t="str">
-        <v>humid</v>
+        <v>/humid/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>湿的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>conceal</v>
       </c>
       <c r="B50" t="str">
-        <v>conceal</v>
+        <v>/conceal/</v>
       </c>
       <c r="C50" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D50" t="str">
         <v>隐藏</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>themselves</v>
       </c>
       <c r="B51" t="str">
-        <v>themselves</v>
+        <v>/themselves/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>他们自己</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>